--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ene-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1285,7 +1285,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
@@ -673,11 +673,7 @@
           <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Aysén</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -734,11 +730,7 @@
           <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -914,7 +906,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1832,11 +1824,7 @@
           <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
@@ -627,7 +627,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -741,7 +749,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -802,7 +814,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -863,7 +879,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -924,7 +944,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -985,7 +1009,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1046,7 +1074,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1107,7 +1139,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1168,7 +1204,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1229,7 +1269,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1290,7 +1334,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1351,7 +1399,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1412,7 +1464,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1473,7 +1529,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1534,7 +1594,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1595,7 +1659,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1656,7 +1724,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1717,7 +1789,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1778,7 +1854,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1835,7 +1915,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1896,7 +1980,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1957,7 +2045,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2018,7 +2110,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2079,7 +2175,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2140,7 +2240,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2201,7 +2305,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2262,7 +2370,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2323,7 +2435,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
+++ b/docs/oc-mensuales/seguro-colectivo-de-vida-con-adicional-de-salud/ene-2025.xlsx
@@ -677,7 +677,11 @@
           <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -738,7 +742,11 @@
           <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
@@ -926,7 +934,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1904,7 +1912,11 @@
           <t>SUBSECRETARIA DE RELACIONES ECONOMICAS INTERNACIONALES</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>BCI SEGUROS VIDA S A</t>
